--- a/BVSimulationFiles/78.xlsx
+++ b/BVSimulationFiles/78.xlsx
@@ -1,38 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cbnor\Documents\Full Body Flow Model Project\BVSimulationFiles\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8499219D-5BE8-4E52-97C7-CB21660DAD84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -51,21 +46,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -353,200 +407,204 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:U3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="B1">
+    <row r="1">
+      <c r="B1" t="n">
         <v>0</v>
       </c>
-      <c r="C1">
-        <v>5.2249999999999998E-2</v>
-      </c>
-      <c r="D1">
+      <c r="C1" t="n">
+        <v>0.05225</v>
+      </c>
+      <c r="D1" t="n">
         <v>0.1045</v>
       </c>
-      <c r="E1">
+      <c r="E1" t="n">
         <v>0.15675</v>
       </c>
-      <c r="F1">
-        <v>0.20899999999999999</v>
-      </c>
-      <c r="G1">
-        <v>0.26124999999999998</v>
-      </c>
-      <c r="H1">
+      <c r="F1" t="n">
+        <v>0.209</v>
+      </c>
+      <c r="G1" t="n">
+        <v>0.26125</v>
+      </c>
+      <c r="H1" t="n">
         <v>0.3135</v>
       </c>
-      <c r="I1">
-        <v>0.36575000000000002</v>
-      </c>
-      <c r="J1">
-        <v>0.41799999999999998</v>
-      </c>
-      <c r="K1">
-        <v>0.47025000000000011</v>
-      </c>
-      <c r="L1">
-        <v>0.52250000000000008</v>
-      </c>
-      <c r="M1">
-        <v>0.57475000000000009</v>
-      </c>
-      <c r="N1">
+      <c r="I1" t="n">
+        <v>0.36575</v>
+      </c>
+      <c r="J1" t="n">
+        <v>0.418</v>
+      </c>
+      <c r="K1" t="n">
+        <v>0.4702500000000001</v>
+      </c>
+      <c r="L1" t="n">
+        <v>0.5225000000000001</v>
+      </c>
+      <c r="M1" t="n">
+        <v>0.5747500000000001</v>
+      </c>
+      <c r="N1" t="n">
         <v>0.627</v>
       </c>
-      <c r="O1">
-        <v>0.67925000000000013</v>
-      </c>
-      <c r="P1">
-        <v>0.73150000000000004</v>
-      </c>
-      <c r="Q1">
-        <v>0.78375000000000017</v>
-      </c>
-      <c r="R1">
-        <v>0.83600000000000008</v>
-      </c>
-      <c r="S1">
-        <v>0.88824999999999998</v>
-      </c>
-      <c r="T1">
-        <v>0.94050000000000011</v>
-      </c>
-      <c r="U1">
-        <v>0.99275000000000002</v>
+      <c r="O1" t="n">
+        <v>0.6792500000000001</v>
+      </c>
+      <c r="P1" t="n">
+        <v>0.7315</v>
+      </c>
+      <c r="Q1" t="n">
+        <v>0.7837500000000002</v>
+      </c>
+      <c r="R1" t="n">
+        <v>0.8360000000000001</v>
+      </c>
+      <c r="S1" t="n">
+        <v>0.88825</v>
+      </c>
+      <c r="T1" t="n">
+        <v>0.9405000000000001</v>
+      </c>
+      <c r="U1" t="n">
+        <v>0.99275</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A2">
+    <row r="2">
+      <c r="A2" t="n">
         <v>0</v>
       </c>
-      <c r="B2">
-        <v>8.4507042253521142E-4</v>
-      </c>
-      <c r="C2">
-        <v>8.0182424511702382E-4</v>
-      </c>
-      <c r="D2">
-        <v>7.6075422989149775E-4</v>
-      </c>
-      <c r="E2">
-        <v>7.21753282450435E-4</v>
-      </c>
-      <c r="F2">
-        <v>6.8471941878747809E-4</v>
-      </c>
-      <c r="G2">
-        <v>6.4955553229216977E-4</v>
-      </c>
-      <c r="H2">
-        <v>6.1616917060812416E-4</v>
-      </c>
-      <c r="I2">
-        <v>5.8447232199336301E-4</v>
-      </c>
-      <c r="J2">
-        <v>5.5438121082975183E-4</v>
-      </c>
-      <c r="K2">
-        <v>5.258161019375564E-4</v>
-      </c>
-      <c r="L2">
-        <v>4.9870111336033321E-4</v>
-      </c>
-      <c r="M2">
-        <v>4.7296403729466311E-4</v>
-      </c>
-      <c r="N2">
-        <v>4.4853616884856819E-4</v>
-      </c>
-      <c r="O2">
-        <v>4.253521423217954E-4</v>
-      </c>
-      <c r="P2">
-        <v>4.0334977471046462E-4</v>
-      </c>
-      <c r="Q2">
-        <v>3.8246991614784652E-4</v>
-      </c>
-      <c r="R2">
-        <v>3.6265630700222512E-4</v>
-      </c>
-      <c r="S2">
-        <v>3.4385544136188438E-4</v>
-      </c>
-      <c r="T2">
-        <v>3.2601643664623289E-4</v>
-      </c>
-      <c r="U2">
-        <v>3.0909090909090909E-4</v>
+      <c r="B2" t="n">
+        <v>0.001690140845070423</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.001603648490234048</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.001521508459782996</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.00144350656490087</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.001369438837574956</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.00129911106458434</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.001232338341216248</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.001168944643986726</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.001108762421659504</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.001051632203875113</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.0009974022267206664</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.0009459280745893262</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.0008970723376971364</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.0008507042846435908</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.0008066995494209292</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.000764939832295693</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.0007253126140044502</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.0006877108827237688</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.0006520328732924658</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.0006181818181818182</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>0.95499999999999996</v>
-      </c>
-      <c r="B3">
-        <v>8.4507042253521142E-4</v>
-      </c>
-      <c r="C3">
-        <v>8.0182424511702382E-4</v>
-      </c>
-      <c r="D3">
-        <v>7.6075422989149775E-4</v>
-      </c>
-      <c r="E3">
-        <v>7.21753282450435E-4</v>
-      </c>
-      <c r="F3">
-        <v>6.8471941878747809E-4</v>
-      </c>
-      <c r="G3">
-        <v>6.4955553229216977E-4</v>
-      </c>
-      <c r="H3">
-        <v>6.1616917060812416E-4</v>
-      </c>
-      <c r="I3">
-        <v>5.8447232199336301E-4</v>
-      </c>
-      <c r="J3">
-        <v>5.5438121082975183E-4</v>
-      </c>
-      <c r="K3">
-        <v>5.258161019375564E-4</v>
-      </c>
-      <c r="L3">
-        <v>4.9870111336033321E-4</v>
-      </c>
-      <c r="M3">
-        <v>4.7296403729466311E-4</v>
-      </c>
-      <c r="N3">
-        <v>4.4853616884856819E-4</v>
-      </c>
-      <c r="O3">
-        <v>4.253521423217954E-4</v>
-      </c>
-      <c r="P3">
-        <v>4.0334977471046462E-4</v>
-      </c>
-      <c r="Q3">
-        <v>3.8246991614784652E-4</v>
-      </c>
-      <c r="R3">
-        <v>3.6265630700222512E-4</v>
-      </c>
-      <c r="S3">
-        <v>3.4385544136188438E-4</v>
-      </c>
-      <c r="T3">
-        <v>3.2601643664623289E-4</v>
-      </c>
-      <c r="U3">
-        <v>3.0909090909090909E-4</v>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>0.955</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.001690140845070423</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.001603648490234048</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.001521508459782996</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.00144350656490087</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.001369438837574956</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.00129911106458434</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.001232338341216248</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.001168944643986726</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.001108762421659504</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.001051632203875113</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.0009974022267206664</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.0009459280745893262</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.0008970723376971364</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.0008507042846435908</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.0008066995494209292</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.000764939832295693</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.0007253126140044502</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.0006877108827237688</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.0006520328732924658</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.0006181818181818182</v>
       </c>
     </row>
   </sheetData>

--- a/BVSimulationFiles/78.xlsx
+++ b/BVSimulationFiles/78.xlsx
@@ -482,64 +482,64 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.001690140845070423</v>
+        <v>0.01690140845070423</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001603648490234048</v>
+        <v>0.01603648490234048</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001521508459782996</v>
+        <v>0.01521508459782996</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00144350656490087</v>
+        <v>0.0144350656490087</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001369438837574956</v>
+        <v>0.01369438837574956</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00129911106458434</v>
+        <v>0.0129911106458434</v>
       </c>
       <c r="H2" t="n">
-        <v>0.001232338341216248</v>
+        <v>0.01232338341216248</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001168944643986726</v>
+        <v>0.01168944643986726</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001108762421659504</v>
+        <v>0.01108762421659504</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001051632203875113</v>
+        <v>0.01051632203875113</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0009974022267206664</v>
+        <v>0.009974022267206664</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0009459280745893262</v>
+        <v>0.009459280745893263</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0008970723376971364</v>
+        <v>0.008970723376971364</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0008507042846435908</v>
+        <v>0.008507042846435909</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0008066995494209292</v>
+        <v>0.008066995494209292</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.000764939832295693</v>
+        <v>0.00764939832295693</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0007253126140044502</v>
+        <v>0.007253126140044502</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0006877108827237688</v>
+        <v>0.006877108827237688</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0006520328732924658</v>
+        <v>0.006520328732924657</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0006181818181818182</v>
+        <v>0.006181818181818182</v>
       </c>
     </row>
     <row r="3">
@@ -547,64 +547,64 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.001690140845070423</v>
+        <v>0.01690140845070423</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001603648490234048</v>
+        <v>0.01603648490234048</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001521508459782996</v>
+        <v>0.01521508459782996</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00144350656490087</v>
+        <v>0.0144350656490087</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001369438837574956</v>
+        <v>0.01369438837574956</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00129911106458434</v>
+        <v>0.0129911106458434</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001232338341216248</v>
+        <v>0.01232338341216248</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001168944643986726</v>
+        <v>0.01168944643986726</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001108762421659504</v>
+        <v>0.01108762421659504</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001051632203875113</v>
+        <v>0.01051632203875113</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0009974022267206664</v>
+        <v>0.009974022267206664</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0009459280745893262</v>
+        <v>0.009459280745893263</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0008970723376971364</v>
+        <v>0.008970723376971364</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0008507042846435908</v>
+        <v>0.008507042846435909</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0008066995494209292</v>
+        <v>0.008066995494209292</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.000764939832295693</v>
+        <v>0.00764939832295693</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0007253126140044502</v>
+        <v>0.007253126140044502</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0006877108827237688</v>
+        <v>0.006877108827237688</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0006520328732924658</v>
+        <v>0.006520328732924657</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0006181818181818182</v>
+        <v>0.006181818181818182</v>
       </c>
     </row>
   </sheetData>

--- a/BVSimulationFiles/78.xlsx
+++ b/BVSimulationFiles/78.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -49,7 +50,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -412,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U3"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -420,61 +421,37 @@
         <v>0</v>
       </c>
       <c r="C1" t="n">
-        <v>0.05225</v>
+        <v>0.03423275862068966</v>
       </c>
       <c r="D1" t="n">
-        <v>0.1045</v>
+        <v>0.06846551724137932</v>
       </c>
       <c r="E1" t="n">
-        <v>0.15675</v>
+        <v>0.102698275862069</v>
       </c>
       <c r="F1" t="n">
-        <v>0.209</v>
+        <v>0.1369310344827586</v>
       </c>
       <c r="G1" t="n">
-        <v>0.26125</v>
+        <v>0.1711637931034483</v>
       </c>
       <c r="H1" t="n">
-        <v>0.3135</v>
+        <v>0.205396551724138</v>
       </c>
       <c r="I1" t="n">
-        <v>0.36575</v>
+        <v>0.2396293103448276</v>
       </c>
       <c r="J1" t="n">
-        <v>0.418</v>
+        <v>0.2738620689655173</v>
       </c>
       <c r="K1" t="n">
-        <v>0.4702500000000001</v>
+        <v>0.3080948275862069</v>
       </c>
       <c r="L1" t="n">
-        <v>0.5225000000000001</v>
+        <v>0.3423275862068966</v>
       </c>
       <c r="M1" t="n">
-        <v>0.5747500000000001</v>
-      </c>
-      <c r="N1" t="n">
-        <v>0.627</v>
-      </c>
-      <c r="O1" t="n">
-        <v>0.6792500000000001</v>
-      </c>
-      <c r="P1" t="n">
-        <v>0.7315</v>
-      </c>
-      <c r="Q1" t="n">
-        <v>0.7837500000000002</v>
-      </c>
-      <c r="R1" t="n">
-        <v>0.8360000000000001</v>
-      </c>
-      <c r="S1" t="n">
-        <v>0.88825</v>
-      </c>
-      <c r="T1" t="n">
-        <v>0.9405000000000001</v>
-      </c>
-      <c r="U1" t="n">
-        <v>0.99275</v>
+        <v>0.3765603448275863</v>
       </c>
     </row>
     <row r="2">
@@ -482,64 +459,40 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01690140845070423</v>
+        <v>0.09306008404051004</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01603648490234048</v>
+        <v>0.08712094250405063</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01521508459782996</v>
+        <v>0.08154914205581296</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0144350656490087</v>
+        <v>0.07632299424466969</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01369438837574956</v>
+        <v>0.07142199721522528</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0129911106458434</v>
+        <v>0.06682677974438569</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01232338341216248</v>
+        <v>0.06251904699571123</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01168944643986726</v>
+        <v>0.05848152804883829</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01108762421659504</v>
+        <v>0.05469792524299073</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01051632203875113</v>
+        <v>0.05115286535774989</v>
       </c>
       <c r="L2" t="n">
-        <v>0.009974022267206664</v>
+        <v>0.04783185264056444</v>
       </c>
       <c r="M2" t="n">
-        <v>0.009459280745893263</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.008970723376971364</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0.008507042846435909</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0.008066995494209292</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0.00764939832295693</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.007253126140044502</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0.006877108827237688</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0.006520328732924657</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0.006181818181818182</v>
+        <v>0.04472122367871439</v>
       </c>
     </row>
     <row r="3">
@@ -547,64 +500,40 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.01690140845070423</v>
+        <v>0.09306008404051004</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01603648490234048</v>
+        <v>0.08712094250405063</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01521508459782996</v>
+        <v>0.08154914205581296</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0144350656490087</v>
+        <v>0.07632299424466969</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01369438837574956</v>
+        <v>0.07142199721522528</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0129911106458434</v>
+        <v>0.06682677974438569</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01232338341216248</v>
+        <v>0.06251904699571123</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01168944643986726</v>
+        <v>0.05848152804883829</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01108762421659504</v>
+        <v>0.05469792524299073</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01051632203875113</v>
+        <v>0.05115286535774989</v>
       </c>
       <c r="L3" t="n">
-        <v>0.009974022267206664</v>
+        <v>0.04783185264056444</v>
       </c>
       <c r="M3" t="n">
-        <v>0.009459280745893263</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.008970723376971364</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0.008507042846435909</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0.008066995494209292</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0.00764939832295693</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0.007253126140044502</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0.006877108827237688</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0.006520328732924657</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0.006181818181818182</v>
+        <v>0.04472122367871439</v>
       </c>
     </row>
   </sheetData>
